--- a/协作/04-进度报告.xlsx
+++ b/协作/04-进度报告.xlsx
@@ -465,7 +465,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H5"/>
+  <dimension ref="A1:H7"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="16" customWidth="1" min="1" max="1"/>
@@ -688,9 +688,93 @@
         </is>
       </c>
     </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>2026-10-18 02:20:00 +08:00</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>切片-0003</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>进行中</t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>协议升到 v3.5：删档位/开关/可选，37+3 全量；补齐 14 份缺失交付物</t>
+        </is>
+      </c>
+      <c r="E6" t="inlineStr">
+        <is>
+          <t>记录追加与快照</t>
+        </is>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>无</t>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>提交并打标签</t>
+        </is>
+      </c>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>约 2 小时</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>2026-10-18 02:40:00 +08:00</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>切片-0003</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>已完成</t>
+        </is>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>37+3 交付物齐全；模板 40 份枚举对齐；快照-0002 还原验证通过</t>
+        </is>
+      </c>
+      <c r="E7" t="inlineStr">
+        <is>
+          <t>无</t>
+        </is>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>无</t>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>推送并重建交付包</t>
+        </is>
+      </c>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <dataValidations count="1">
-    <dataValidation sqref="C2:C121" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" errorTitle="取值不合法" error="只能选择下拉里的值" type="list">
+    <dataValidation sqref="C2:C121" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
       <formula1>"待派工,进行中,审查中,验证中,集成中,已完成,阻塞"</formula1>
     </dataValidation>
   </dataValidations>

--- a/协作/04-进度报告.xlsx
+++ b/协作/04-进度报告.xlsx
@@ -465,7 +465,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H7"/>
+  <dimension ref="A1:H9"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="16" customWidth="1" min="1" max="1"/>
@@ -767,6 +767,90 @@
         </is>
       </c>
       <c r="H7" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>2026-10-18 03:30:00 +08:00</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>切片-0004</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>进行中</t>
+        </is>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>TEAMODEL 仓库建立并推送（main a3850b9，tag tm-v3.5.1）；DCG 移除 TEAMODEL.md 与 协作/模板/</t>
+        </is>
+      </c>
+      <c r="E8" t="inlineStr">
+        <is>
+          <t>引用登记、画像更新、证据</t>
+        </is>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>无</t>
+        </is>
+      </c>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>补证据与记录</t>
+        </is>
+      </c>
+      <c r="H8" t="inlineStr">
+        <is>
+          <t>约 40 分钟</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>2026-10-18 03:45:00 +08:00</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>切片-0004</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>已完成</t>
+        </is>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>移除完成；模板转入 .gitignore 作为本地缓存；记录与证据补齐</t>
+        </is>
+      </c>
+      <c r="E9" t="inlineStr">
+        <is>
+          <t>无</t>
+        </is>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>无</t>
+        </is>
+      </c>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>提交并推送</t>
+        </is>
+      </c>
+      <c r="H9" t="inlineStr">
         <is>
           <t>0</t>
         </is>

--- a/协作/04-进度报告.xlsx
+++ b/协作/04-进度报告.xlsx
@@ -465,7 +465,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H9"/>
+  <dimension ref="A1:H11"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="16" customWidth="1" min="1" max="1"/>
@@ -851,6 +851,90 @@
         </is>
       </c>
       <c r="H9" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>2026-10-18 04:05:00 +08:00</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>切片-0005</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>进行中</t>
+        </is>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>标题与状态段已改</t>
+        </is>
+      </c>
+      <c r="E10" t="inlineStr">
+        <is>
+          <t>适配场景章节撰写</t>
+        </is>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>无</t>
+        </is>
+      </c>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>补 0.3 约束与实据列</t>
+        </is>
+      </c>
+      <c r="H10" t="inlineStr">
+        <is>
+          <t>约 20 分钟</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>2026-10-18 04:20:00 +08:00</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>切片-0005</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>已完成</t>
+        </is>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>README 修订完成；pytest 696 passed；accept 16 PASS</t>
+        </is>
+      </c>
+      <c r="E11" t="inlineStr">
+        <is>
+          <t>无</t>
+        </is>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>无</t>
+        </is>
+      </c>
+      <c r="G11" t="inlineStr">
+        <is>
+          <t>记账并提交</t>
+        </is>
+      </c>
+      <c r="H11" t="inlineStr">
         <is>
           <t>0</t>
         </is>

--- a/协作/04-进度报告.xlsx
+++ b/协作/04-进度报告.xlsx
@@ -465,7 +465,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H11"/>
+  <dimension ref="A1:H13"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="16" customWidth="1" min="1" max="1"/>
@@ -935,6 +935,90 @@
         </is>
       </c>
       <c r="H11" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>2026-10-18 04:28:00 +08:00</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>切片-0006</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>进行中</t>
+        </is>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>开篇与 §0 主场景已改</t>
+        </is>
+      </c>
+      <c r="E12" t="inlineStr">
+        <is>
+          <t>补 0.1 首行</t>
+        </is>
+      </c>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t>无</t>
+        </is>
+      </c>
+      <c r="G12" t="inlineStr">
+        <is>
+          <t>跑回归并记账</t>
+        </is>
+      </c>
+      <c r="H12" t="inlineStr">
+        <is>
+          <t>约 10 分钟</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>2026-10-18 04:40:00 +08:00</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>切片-0006</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>已完成</t>
+        </is>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>README 定位修订完成；pytest 696 passed；accept 16 PASS</t>
+        </is>
+      </c>
+      <c r="E13" t="inlineStr">
+        <is>
+          <t>无</t>
+        </is>
+      </c>
+      <c r="F13" t="inlineStr">
+        <is>
+          <t>无</t>
+        </is>
+      </c>
+      <c r="G13" t="inlineStr">
+        <is>
+          <t>记账并提交</t>
+        </is>
+      </c>
+      <c r="H13" t="inlineStr">
         <is>
           <t>0</t>
         </is>

--- a/协作/04-进度报告.xlsx
+++ b/协作/04-进度报告.xlsx
@@ -465,7 +465,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H13"/>
+  <dimension ref="A1:H15"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="16" customWidth="1" min="1" max="1"/>
@@ -1019,6 +1019,90 @@
         </is>
       </c>
       <c r="H13" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>2026-10-18 04:48:00 +08:00</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>切片-0007</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>进行中</t>
+        </is>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>引用块已删</t>
+        </is>
+      </c>
+      <c r="E14" t="inlineStr">
+        <is>
+          <t>删 §0 子节并核对交叉引用</t>
+        </is>
+      </c>
+      <c r="F14" t="inlineStr">
+        <is>
+          <t>无</t>
+        </is>
+      </c>
+      <c r="G14" t="inlineStr">
+        <is>
+          <t>跑回归并记账</t>
+        </is>
+      </c>
+      <c r="H14" t="inlineStr">
+        <is>
+          <t>约 10 分钟</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>2026-10-18 04:55:00 +08:00</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>切片-0007</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>已完成</t>
+        </is>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>README 精简完成；pytest 696 passed；accept 16 PASS</t>
+        </is>
+      </c>
+      <c r="E15" t="inlineStr">
+        <is>
+          <t>无</t>
+        </is>
+      </c>
+      <c r="F15" t="inlineStr">
+        <is>
+          <t>无</t>
+        </is>
+      </c>
+      <c r="G15" t="inlineStr">
+        <is>
+          <t>记账并提交</t>
+        </is>
+      </c>
+      <c r="H15" t="inlineStr">
         <is>
           <t>0</t>
         </is>
